--- a/docs/Consolidados_febrero/Consolidado GP-F-23_ODS 90577837_Febrero.xlsx
+++ b/docs/Consolidados_febrero/Consolidado GP-F-23_ODS 90577837_Febrero.xlsx
@@ -378,7 +378,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,8 +451,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,6 +483,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -707,7 +731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,9 +847,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -838,49 +907,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -936,7 +1017,7 @@
         <xdr:cNvPr id="2" name="Picture 17" descr="logo_meridian">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1010,7 +1091,7 @@
         <xdr:cNvPr id="3" name="Picture 17" descr="logo_meridian">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1089,7 +1170,7 @@
         <xdr:cNvPr id="2" name="Picture 17" descr="logo_meridian">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1163,7 +1244,7 @@
         <xdr:cNvPr id="3" name="Picture 17" descr="logo_meridian">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1486,68 +1567,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.36328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.6328125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.453125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="2" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="3" customWidth="1"/>
     <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="16.453125" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.6328125" style="3"/>
+    <col min="17" max="17" width="16.42578125" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="8.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="P1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="P2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="47" t="s">
+    <row r="3" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48" t="s">
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="J3" s="63"/>
+      <c r="K3" s="64"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="K4" s="6"/>
@@ -1555,11 +1635,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:16" s="11" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="45" t="s">
+    <row r="5" spans="2:16" s="11" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="45"/>
+      <c r="C5" s="59"/>
       <c r="D5" s="7">
         <v>90577837</v>
       </c>
@@ -1575,7 +1655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1591,11 +1671,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="45" t="s">
+    <row r="7" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="45"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="13" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
       <c r="D8" s="14"/>
@@ -1627,11 +1707,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="45" t="s">
+    <row r="9" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="45"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="17">
         <v>46053</v>
       </c>
@@ -1647,7 +1727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
       <c r="E10"/>
@@ -1659,28 +1739,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="26.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="50" t="s">
+    <row r="11" spans="2:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="45" t="s">
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="45"/>
+      <c r="K11" s="59"/>
       <c r="P11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>22</v>
       </c>
@@ -1715,7 +1795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="46" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B13" s="22">
         <v>7</v>
       </c>
@@ -1750,7 +1830,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="23" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B14" s="27">
         <v>7</v>
       </c>
@@ -1785,7 +1865,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="27">
         <v>7</v>
       </c>
@@ -1820,24 +1900,24 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="51" t="str">
+      <c r="G16" s="60" t="str">
         <f>+CONCATENATE("TOTAL A ",D7)</f>
         <v>TOTAL A ENERO</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51" t="s">
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="51"/>
-    </row>
-    <row r="17" spans="1:16" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K16" s="60"/>
+    </row>
+    <row r="17" spans="1:16" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="G17" s="37">
@@ -1863,49 +1943,49 @@
       <c r="N17"/>
       <c r="P17"/>
     </row>
-    <row r="19" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="50" t="s">
+    <row r="19" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
-    </row>
-    <row r="20" spans="1:16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+    </row>
+    <row r="20" spans="1:16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39"/>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="59"/>
-    </row>
-    <row r="21" spans="1:16" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="53"/>
+    </row>
+    <row r="21" spans="1:16" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="62"/>
-    </row>
-    <row r="22" spans="1:16" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="56"/>
+    </row>
+    <row r="22" spans="1:16" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="40" t="s">
         <v>36</v>
       </c>
@@ -1919,63 +1999,63 @@
       <c r="J22" s="41"/>
       <c r="K22" s="42"/>
     </row>
-    <row r="23" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="43" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="44"/>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-    </row>
-    <row r="24" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+    </row>
+    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="44"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B25" s="64" t="s">
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
         <v>39</v>
       </c>
@@ -1989,61 +2069,61 @@
       <c r="J27" s="41"/>
       <c r="K27" s="42"/>
     </row>
-    <row r="28" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="43" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="44"/>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-    </row>
-    <row r="29" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+    </row>
+    <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="44"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-    </row>
-    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-    </row>
-    <row r="33" spans="2:10" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+    </row>
+    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+    </row>
+    <row r="33" spans="2:10" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
       <c r="G33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H33" s="54" t="s">
+      <c r="H33" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-    </row>
-    <row r="65" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+    </row>
+    <row r="65" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2055,7 +2135,7 @@
       <c r="P65"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2067,7 +2147,7 @@
       <c r="P66"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2079,7 +2159,7 @@
       <c r="P67"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2091,7 +2171,7 @@
       <c r="P68"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -2103,7 +2183,7 @@
       <c r="P69"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -2115,7 +2195,7 @@
       <c r="P70"/>
       <c r="Q70" s="3"/>
     </row>
-    <row r="71" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2127,7 +2207,7 @@
       <c r="P71"/>
       <c r="Q71" s="3"/>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -2139,7 +2219,7 @@
       <c r="P72"/>
       <c r="Q72" s="3"/>
     </row>
-    <row r="73" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -2151,7 +2231,7 @@
       <c r="P73"/>
       <c r="Q73" s="3"/>
     </row>
-    <row r="74" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -2163,7 +2243,7 @@
       <c r="P74"/>
       <c r="Q74" s="3"/>
     </row>
-    <row r="75" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -2175,7 +2255,7 @@
       <c r="P75"/>
       <c r="Q75" s="3"/>
     </row>
-    <row r="76" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -2187,7 +2267,7 @@
       <c r="P76"/>
       <c r="Q76" s="3"/>
     </row>
-    <row r="77" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>31</v>
       </c>
@@ -2202,6 +2282,18 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="22">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="C33:D33"/>
@@ -2212,18 +2304,6 @@
     <mergeCell ref="D23:K24"/>
     <mergeCell ref="B25:K26"/>
     <mergeCell ref="D28:K29"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <conditionalFormatting sqref="G17">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
@@ -2256,68 +2336,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.36328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.6328125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.453125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="2" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="3" customWidth="1"/>
     <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="16.453125" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.6328125" style="3"/>
+    <col min="17" max="17" width="16.42578125" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="8.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="P1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
       <c r="P2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="47" t="s">
+    <row r="3" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48" t="s">
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48" t="s">
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="J3" s="63"/>
+      <c r="K3" s="64"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="K4" s="6"/>
@@ -2325,12 +2404,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:16" s="11" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="45" t="s">
+    <row r="5" spans="2:16" s="11" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="7">
+      <c r="C5" s="59"/>
+      <c r="D5" s="72">
         <v>90577837</v>
       </c>
       <c r="E5" s="8"/>
@@ -2345,7 +2424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -2361,11 +2440,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="45" t="s">
+    <row r="7" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="45"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="13" t="s">
         <v>6</v>
       </c>
@@ -2381,7 +2460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
       <c r="D8" s="14"/>
@@ -2397,11 +2476,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="45" t="s">
+    <row r="9" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="45"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="17">
         <v>46081</v>
       </c>
@@ -2417,7 +2496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
       <c r="E10"/>
@@ -2429,28 +2508,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="26.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="50" t="s">
+    <row r="11" spans="2:16" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="45" t="s">
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="45"/>
+      <c r="K11" s="59"/>
       <c r="P11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>22</v>
       </c>
@@ -2485,49 +2564,49 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="46" x14ac:dyDescent="0.35">
-      <c r="B13" s="22">
+    <row r="13" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B13" s="65">
         <v>7</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="66">
         <v>80</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="69">
         <v>10</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="70">
         <f>IFERROR(H13/G13,0)</f>
         <v>0.125</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="71">
         <f>+H13+ENERO!J13</f>
         <v>20</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="70">
         <f>IFERROR(J13/G13,0)</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="23" x14ac:dyDescent="0.35">
-      <c r="B14" s="27">
+    <row r="14" spans="2:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="80">
         <v>7</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="82" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="29" t="s">
@@ -2536,7 +2615,7 @@
       <c r="F14" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="83">
         <v>80</v>
       </c>
       <c r="H14" s="32">
@@ -2555,14 +2634,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="27">
+    <row r="15" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="81">
         <v>7</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="82" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="29" t="s">
@@ -2571,7 +2650,7 @@
       <c r="F15" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="81">
         <v>80</v>
       </c>
       <c r="H15" s="35">
@@ -2590,24 +2669,24 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="51" t="str">
+      <c r="G16" s="60" t="str">
         <f>+CONCATENATE("TOTAL A ",D7)</f>
         <v>TOTAL A FEBRERO</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51" t="s">
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="51"/>
-    </row>
-    <row r="17" spans="1:16" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K16" s="60"/>
+    </row>
+    <row r="17" spans="1:16" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="G17" s="37">
@@ -2633,49 +2712,49 @@
       <c r="N17"/>
       <c r="P17"/>
     </row>
-    <row r="19" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="50" t="s">
+    <row r="19" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
-    </row>
-    <row r="20" spans="1:16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+    </row>
+    <row r="20" spans="1:16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39"/>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="59"/>
-    </row>
-    <row r="21" spans="1:16" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="75"/>
+    </row>
+    <row r="21" spans="1:16" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="62"/>
-    </row>
-    <row r="22" spans="1:16" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="76"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="78"/>
+    </row>
+    <row r="22" spans="1:16" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="40" t="s">
         <v>36</v>
       </c>
@@ -2689,63 +2768,63 @@
       <c r="J22" s="41"/>
       <c r="K22" s="42"/>
     </row>
-    <row r="23" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="43" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="44"/>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-    </row>
-    <row r="24" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+    </row>
+    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="44"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B25" s="64" t="s">
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
         <v>39</v>
       </c>
@@ -2759,61 +2838,61 @@
       <c r="J27" s="41"/>
       <c r="K27" s="42"/>
     </row>
-    <row r="28" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="43" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="44"/>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-    </row>
-    <row r="29" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+    </row>
+    <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="44"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-    </row>
-    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-    </row>
-    <row r="33" spans="2:10" ht="23.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+    </row>
+    <row r="32" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+    </row>
+    <row r="33" spans="2:10" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
       <c r="G33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H33" s="54" t="s">
+      <c r="H33" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-    </row>
-    <row r="65" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+    </row>
+    <row r="65" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2825,7 +2904,7 @@
       <c r="P65"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2837,7 +2916,7 @@
       <c r="P66"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2849,7 +2928,7 @@
       <c r="P67"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -2861,7 +2940,7 @@
       <c r="P68"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -2873,7 +2952,7 @@
       <c r="P69"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -2885,7 +2964,7 @@
       <c r="P70"/>
       <c r="Q70" s="3"/>
     </row>
-    <row r="71" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2897,7 +2976,7 @@
       <c r="P71"/>
       <c r="Q71" s="3"/>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -2909,7 +2988,7 @@
       <c r="P72"/>
       <c r="Q72" s="3"/>
     </row>
-    <row r="73" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -2921,7 +3000,7 @@
       <c r="P73"/>
       <c r="Q73" s="3"/>
     </row>
-    <row r="74" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -2933,7 +3012,7 @@
       <c r="P74"/>
       <c r="Q74" s="3"/>
     </row>
-    <row r="75" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -2945,7 +3024,7 @@
       <c r="P75"/>
       <c r="Q75" s="3"/>
     </row>
-    <row r="76" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -2957,7 +3036,7 @@
       <c r="P76"/>
       <c r="Q76" s="3"/>
     </row>
-    <row r="77" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>31</v>
       </c>
@@ -2972,6 +3051,18 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="22">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="C33:D33"/>
@@ -2982,18 +3073,6 @@
     <mergeCell ref="D23:K24"/>
     <mergeCell ref="B25:K26"/>
     <mergeCell ref="D28:K29"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <conditionalFormatting sqref="G17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
